--- a/astro-site/public/dl/restaurant-checklist-templates/07-blank-checklist-template.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/07-blank-checklist-template.xlsx
@@ -876,7 +876,7 @@
     <row r="41" ht="31" customHeight="1">
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
